--- a/template.xlsx
+++ b/template.xlsx
@@ -29,31 +29,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Wuxi Bewis Sensing Technology LLC</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">            </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="30"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> Quote</t>
-    </r>
+    <t xml:space="preserve">             Quote</t>
   </si>
   <si>
     <t>Date:</t>
   </si>
   <si>
-    <t>June,27th.2025</t>
+    <t>May, 14th. 2026</t>
   </si>
   <si>
     <t>Valid Until:</t>
@@ -65,7 +52,7 @@
     <t>Quote Number:</t>
   </si>
   <si>
-    <t>Bewis-MC-0627-AU</t>
+    <t>20260514-MC-BD</t>
   </si>
   <si>
     <t>Customer ID</t>
@@ -83,8 +70,7 @@
     <t>Name:</t>
   </si>
   <si>
-    <t xml:space="preserve">
-</t>
+    <t/>
   </si>
   <si>
     <t>Customer Contact:</t>
@@ -108,30 +94,8 @@
     <t>Qty(Set)</t>
   </si>
   <si>
-    <r>
-      <t>Unit Price/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="10"/>
-        <rFont val="Sitka Display"/>
-        <charset val="0"/>
-      </rPr>
-      <t>USD</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Sitka Display"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>Unit Price/USD
 (FOB )</t>
-    </r>
   </si>
   <si>
     <t>Line Total</t>
@@ -143,40 +107,7 @@
     <t>Remark</t>
   </si>
   <si>
-    <t>Inclinometer</t>
-  </si>
-  <si>
-    <t>BWS5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual Axis
-Measuring  range ±15°
-Accuracy 0.001°
-Output :RS232，RS485，TTL optional
-</t>
-  </si>
-  <si>
-    <t>BWS2000</t>
-  </si>
-  <si>
-    <t>Dual axis
-Measuring  range ±30°
-Accuracy: 0.001°
-Power supply voltage: 9-36V
-Output: RS232，RS485，TTL optional</t>
-  </si>
-  <si>
-    <t>Wireless Inclinometer</t>
-  </si>
-  <si>
-    <t>LWHD-WM400</t>
-  </si>
-  <si>
-    <t>Dual axis
-Measuring  range ±90°
-Accuracy: 0.01°
-Power supply voltage: 9-36V
-Output: RS232，RS485，TTL optional</t>
+    <t>°</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -185,33 +116,14 @@
     <t>Subtotal</t>
   </si>
   <si>
-    <r>
-      <t>1. Payment Terms-- 
+    <t xml:space="preserve">1. Payment Terms-- 
                      T/T 100% advanced by BEWIS official on-line shop （priority）(≤$5000)
                       Bewis Business Bank Account or L/C Irrevocable at sight（＞$5000）                              
-2. Lead Time--  for</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> sample</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="等线"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> -5-7 working days after the payment
+2. Lead Time--  for sample -5-7 working days after the payment
 3. Quotation Validity-- 1 Month
 4. Package-- Bewis Carton package or your customized package（please inform Bewis in advance）
 5. MOQ-- 1 set
 6. Warranty -- 12months </t>
-    </r>
   </si>
   <si>
     <t>Discount</t>
@@ -259,7 +171,7 @@
     <numFmt numFmtId="176" formatCode="\$#,##0.00;[Red]\-\$#,##0.00"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="40">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -269,7 +181,6 @@
       <b/>
       <sz val="18"/>
       <name val="Calisto MT"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -277,7 +188,6 @@
       <sz val="20"/>
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Calisto MT"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -301,7 +211,6 @@
       <sz val="14"/>
       <color theme="0"/>
       <name val="Calisto MT"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -325,7 +234,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft Tai Le"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
@@ -367,11 +275,6 @@
       <charset val="0"/>
     </font>
     <font>
-      <sz val="14"/>
-      <name val="Sitka Display"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
@@ -388,14 +291,12 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calisto MT"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -403,7 +304,6 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -411,7 +311,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -419,7 +318,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -428,7 +326,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -437,7 +334,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -446,7 +342,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -455,7 +350,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -464,7 +358,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -472,7 +365,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -481,7 +373,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -490,7 +381,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -499,7 +389,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -507,7 +396,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -516,7 +404,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -524,7 +411,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -532,7 +418,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -540,7 +425,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -548,7 +432,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -556,24 +439,8 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="10"/>
-      <name val="Sitka Display"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="30"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="0"/>
     </font>
   </fonts>
   <fills count="35">
@@ -782,7 +649,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -867,6 +734,146 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -891,78 +898,6 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -974,37 +909,7 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1013,19 +918,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1137,450 +1029,308 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="64">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1636,18 +1386,6 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="000066CC"/>
-      <color rgb="000000FF"/>
-      <color rgb="00333333"/>
-      <color rgb="00FF0000"/>
-      <color rgb="002F75B5"/>
-      <color rgb="00A9D08E"/>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00000000"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1695,132 +1433,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>107315</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>213360</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1202690</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1270" name="图片 1" descr="BWS5000"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7753985" y="4588510"/>
-          <a:ext cx="1095375" cy="966470"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>130175</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>373380</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1240155</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>630555</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1271" name="图片 2" descr="BWM426"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7776845" y="8812530"/>
-          <a:ext cx="1109980" cy="981075"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>429895</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1218565</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>5715</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1272" name="图片 3" descr="BWS5000"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7707630" y="6697345"/>
-          <a:ext cx="1157605" cy="1023620"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2089,685 +1702,508 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.9" customWidth="1"/>
-    <col min="2" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="12.575" customWidth="1"/>
-    <col min="6" max="7" width="13.5" customWidth="1"/>
-    <col min="8" max="8" width="17.125" customWidth="1"/>
-    <col min="9" max="9" width="24.375" customWidth="1"/>
-    <col min="12" max="12" width="12.625"/>
+    <col min="1" max="1" width="19.9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.575" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1"/>
     <row r="2" ht="29" customHeight="1" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="13" customHeight="1" spans="1:12">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="A3" s="6"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" ht="19.5" spans="1:12">
+    <row r="4" ht="19.5" customHeight="1" spans="1:12">
       <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="11" t="s">
+      <c r="H4" s="9"/>
+      <c r="I4" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="19.5" spans="1:12">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="G5" s="10" t="s">
+    <row r="5" ht="19.5" customHeight="1" spans="1:12">
+      <c r="A5" s="6"/>
+      <c r="G5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="11" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="19.5" spans="1:12">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="G6" s="12" t="s">
+    <row r="6" ht="19.5" customHeight="1" spans="1:12">
+      <c r="A6" s="6"/>
+      <c r="G6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="13" t="s">
+      <c r="H6" s="11"/>
+      <c r="I6" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="19.5" spans="1:12">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="G7" s="12" t="s">
+    <row r="7" ht="19.5" customHeight="1" spans="1:12">
+      <c r="A7" s="6"/>
+      <c r="G7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="14" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="8" customHeight="1" spans="1:12">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="I8" s="15"/>
+      <c r="A8" s="6"/>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:12">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="19"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:12">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
-      <c r="E10" s="23" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="E10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="25"/>
-    </row>
-    <row r="11" ht="19.5" spans="1:12">
-      <c r="A11" s="26" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="21"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" spans="1:12">
+      <c r="A11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="28"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="31"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="E11" s="6"/>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:12">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="28"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="31"/>
-    </row>
-    <row r="13" ht="19.5" spans="1:12">
-      <c r="A13" s="26" t="s">
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="E12" s="6"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" spans="1:12">
+      <c r="A13" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="31"/>
-    </row>
-    <row r="14" ht="19.5" spans="1:12">
-      <c r="A14" s="26" t="s">
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="E13" s="6"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" spans="1:12">
+      <c r="A14" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="35"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
     </row>
     <row r="15" ht="10" customHeight="1" spans="1:12">
-      <c r="A15" s="36"/>
-      <c r="B15" s="37"/>
-      <c r="I15" s="15"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="I15" s="12"/>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:12">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="H16" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="I16" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40">
+      <c r="K16" s="33"/>
+      <c r="L16" s="33">
         <v>6.8</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:12">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="38">
+        <v>1</v>
+      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40">
+        <v>51.47</v>
+      </c>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42" t="s">
+      <c r="K17" s="33">
+        <v>350</v>
+      </c>
+      <c r="L17" s="43">
+        <f t="shared" ref="L17:L25" si="0">K17/$L$16</f>
+        <v>51.4705882352941</v>
+      </c>
+    </row>
+    <row r="18" ht="57" customHeight="1" spans="1:12">
+      <c r="A18" s="6"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="38">
+        <v>4</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40">
+        <v>2941.16</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="K18" s="33">
+        <v>300</v>
+      </c>
+      <c r="L18" s="43">
+        <f t="shared" si="0"/>
+        <v>44.1176470588235</v>
+      </c>
+    </row>
+    <row r="19" ht="57" customHeight="1" spans="1:12">
+      <c r="A19" s="6"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="38">
+        <v>30</v>
+      </c>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40">
+        <f>E19*F19</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="45"/>
+      <c r="I19" s="44"/>
+      <c r="K19" s="33">
+        <v>200</v>
+      </c>
+      <c r="L19" s="43">
+        <f t="shared" si="0"/>
+        <v>29.4117647058824</v>
+      </c>
+    </row>
+    <row r="20" ht="57" customHeight="1" spans="1:12">
+      <c r="A20" s="6"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="38">
+        <v>1</v>
+      </c>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40">
+        <f>E20*F20</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="38"/>
+      <c r="I20" s="47"/>
+      <c r="K20" s="33">
+        <v>950</v>
+      </c>
+      <c r="L20" s="43">
+        <f t="shared" si="0"/>
+        <v>139.705882352941</v>
+      </c>
+    </row>
+    <row r="21" ht="57" customHeight="1" spans="1:12">
+      <c r="A21" s="6"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="38">
+        <v>10</v>
+      </c>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40">
+        <f>E21*F21</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="44"/>
+      <c r="I21" s="48"/>
+      <c r="K21" s="33">
+        <v>800</v>
+      </c>
+      <c r="L21" s="43">
+        <f t="shared" si="0"/>
+        <v>117.647058823529</v>
+      </c>
+    </row>
+    <row r="22" ht="57" customHeight="1" spans="1:12">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="38">
+        <v>30</v>
+      </c>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40">
+        <f>E22*F22</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="45"/>
+      <c r="I22" s="49"/>
+      <c r="K22" s="33">
+        <v>650</v>
+      </c>
+      <c r="L22" s="43">
+        <f t="shared" si="0"/>
+        <v>95.5882352941177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="50"/>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:12">
+      <c r="A24" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="43">
-        <v>1</v>
-      </c>
-      <c r="F17" s="44">
-        <v>500</v>
-      </c>
-      <c r="G17" s="45">
-        <f t="shared" ref="G17:G19" si="0">E17*F17</f>
-        <v>500</v>
-      </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="47" t="s">
+      <c r="F24" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="40">
-        <v>350</v>
-      </c>
-      <c r="L17" s="48">
-        <f t="shared" ref="L17:L25" si="1">K17/$L$16</f>
-        <v>51.4705882352941</v>
-      </c>
-    </row>
-    <row r="18" ht="57" customHeight="1" spans="1:12">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="43">
-        <v>10</v>
-      </c>
-      <c r="F18" s="44">
-        <v>600</v>
-      </c>
-      <c r="G18" s="45">
-        <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-      <c r="H18" s="51"/>
-      <c r="I18" s="52"/>
-      <c r="K18" s="40">
-        <v>300</v>
-      </c>
-      <c r="L18" s="48">
-        <f t="shared" si="1"/>
-        <v>44.1176470588235</v>
-      </c>
-    </row>
-    <row r="19" ht="57" customHeight="1" spans="1:12">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="43">
+      <c r="G24" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="54"/>
+      <c r="I24" s="24"/>
+    </row>
+    <row r="25" ht="13" customHeight="1" spans="1:12">
+      <c r="A25" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="21"/>
+    </row>
+    <row r="26" ht="13" customHeight="1" spans="1:12">
+      <c r="A26" s="6"/>
+      <c r="E26" s="16"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="29"/>
+    </row>
+    <row r="27" ht="13" customHeight="1" spans="1:12">
+      <c r="A27" s="6"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="44">
-        <v>700</v>
-      </c>
-      <c r="G19" s="45">
-        <f t="shared" si="0"/>
-        <v>21000</v>
-      </c>
-      <c r="H19" s="54"/>
-      <c r="I19" s="52"/>
-      <c r="K19" s="40">
-        <v>200</v>
-      </c>
-      <c r="L19" s="48">
-        <f t="shared" si="1"/>
-        <v>29.4117647058824</v>
-      </c>
-    </row>
-    <row r="20" ht="57" customHeight="1" spans="1:12">
-      <c r="A20" s="49"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="43">
-        <v>1</v>
-      </c>
-      <c r="F20" s="44">
-        <v>800</v>
-      </c>
-      <c r="G20" s="45">
-        <f t="shared" ref="G20:G25" si="2">E20*F20</f>
-        <v>800</v>
-      </c>
-      <c r="H20" s="51"/>
-      <c r="I20" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="40">
-        <v>950</v>
-      </c>
-      <c r="L20" s="48">
-        <f t="shared" si="1"/>
-        <v>139.705882352941</v>
-      </c>
-    </row>
-    <row r="21" ht="57" customHeight="1" spans="1:12">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="43">
-        <v>10</v>
-      </c>
-      <c r="F21" s="44">
-        <v>900</v>
-      </c>
-      <c r="G21" s="45">
-        <f t="shared" si="2"/>
-        <v>9000</v>
-      </c>
-      <c r="H21" s="51"/>
-      <c r="I21" s="56"/>
-      <c r="K21" s="40">
-        <v>800</v>
-      </c>
-      <c r="L21" s="48">
-        <f t="shared" si="1"/>
-        <v>117.647058823529</v>
-      </c>
-    </row>
-    <row r="22" ht="57" customHeight="1" spans="1:12">
-      <c r="A22" s="49"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="43">
-        <v>30</v>
-      </c>
-      <c r="F22" s="44">
-        <v>1100</v>
-      </c>
-      <c r="G22" s="45">
-        <f t="shared" si="2"/>
-        <v>33000</v>
-      </c>
-      <c r="H22" s="54"/>
-      <c r="I22" s="57"/>
-      <c r="K22" s="40">
-        <v>650</v>
-      </c>
-      <c r="L22" s="48">
-        <f t="shared" si="1"/>
-        <v>95.5882352941177</v>
-      </c>
-    </row>
-    <row r="23" ht="57" customHeight="1" spans="1:12">
-      <c r="A23" s="49" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="50" t="s">
+      <c r="G27" s="53"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="21"/>
+    </row>
+    <row r="28" ht="13" customHeight="1" spans="1:12">
+      <c r="A28" s="6"/>
+      <c r="E28" s="16"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="29"/>
+    </row>
+    <row r="29" ht="13" customHeight="1" spans="1:12">
+      <c r="A29" s="6"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="43">
-        <v>1</v>
-      </c>
-      <c r="F23" s="44">
-        <v>1300</v>
-      </c>
-      <c r="G23" s="45">
-        <f t="shared" si="2"/>
-        <v>1300</v>
-      </c>
-      <c r="H23" s="51"/>
-      <c r="I23" s="55" t="s">
+      <c r="G29" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="21"/>
+    </row>
+    <row r="30" ht="13" customHeight="1" spans="1:12">
+      <c r="A30" s="6"/>
+      <c r="E30" s="16"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="29"/>
+    </row>
+    <row r="31" ht="13" customHeight="1" spans="1:12">
+      <c r="A31" s="6"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="40">
-        <v>950</v>
-      </c>
-      <c r="L23" s="48">
-        <f t="shared" si="1"/>
-        <v>139.705882352941</v>
-      </c>
-    </row>
-    <row r="24" ht="57" customHeight="1" spans="1:12">
-      <c r="A24" s="49"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="43">
-        <v>10</v>
-      </c>
-      <c r="F24" s="44">
-        <v>1610</v>
-      </c>
-      <c r="G24" s="45">
-        <f t="shared" si="2"/>
-        <v>16100</v>
-      </c>
-      <c r="H24" s="51"/>
-      <c r="I24" s="56"/>
-      <c r="K24" s="40">
-        <v>800</v>
-      </c>
-      <c r="L24" s="48">
-        <f t="shared" si="1"/>
-        <v>117.647058823529</v>
-      </c>
-    </row>
-    <row r="25" ht="57" customHeight="1" spans="1:12">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="43">
-        <v>100</v>
-      </c>
-      <c r="F25" s="44">
-        <v>1300</v>
-      </c>
-      <c r="G25" s="45">
-        <f t="shared" si="2"/>
-        <v>130000</v>
-      </c>
-      <c r="H25" s="54"/>
-      <c r="I25" s="57"/>
-      <c r="K25" s="40">
-        <v>650</v>
-      </c>
-      <c r="L25" s="48">
-        <f t="shared" si="1"/>
-        <v>95.5882352941177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="59"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" ht="24" spans="1:12">
-      <c r="A27" s="60" t="s">
+      <c r="G31" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="21"/>
+    </row>
+    <row r="32" ht="16" customHeight="1" spans="1:12">
+      <c r="A32" s="6"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="29"/>
+    </row>
+    <row r="33" ht="124" customHeight="1" spans="1:9">
+      <c r="A33" s="6"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="I33" s="16"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1" spans="1:9">
+      <c r="A34" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-    </row>
-    <row r="28" ht="13" customHeight="1" spans="1:12">
-      <c r="A28" s="66" t="s">
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69" t="s">
+      <c r="B35" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="G28" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="71"/>
-      <c r="I28" s="72"/>
-    </row>
-    <row r="29" ht="13" customHeight="1" spans="1:12">
-      <c r="A29" s="73"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="78"/>
-    </row>
-    <row r="30" ht="13" customHeight="1" spans="1:12">
-      <c r="A30" s="73"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="79" t="s">
+      <c r="C35" s="21"/>
+      <c r="D35" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="72"/>
-    </row>
-    <row r="31" ht="13" customHeight="1" spans="1:12">
-      <c r="A31" s="73"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="78"/>
-    </row>
-    <row r="32" ht="13" customHeight="1" spans="1:12">
-      <c r="A32" s="73"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="79" t="s">
+      <c r="E35" s="3"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="71"/>
-      <c r="I32" s="72"/>
-    </row>
-    <row r="33" ht="13" customHeight="1" spans="1:9">
-      <c r="A33" s="73"/>
-      <c r="B33" s="74"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="78"/>
-    </row>
-    <row r="34" ht="13" customHeight="1" spans="1:9">
-      <c r="A34" s="73"/>
-      <c r="B34" s="74"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="79" t="s">
+      <c r="H35" s="54"/>
+      <c r="I35" s="24"/>
+    </row>
+    <row r="36" ht="11" customHeight="1" spans="1:9">
+      <c r="A36" s="45"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="G34" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="71"/>
-      <c r="I34" s="72"/>
-    </row>
-    <row r="35" ht="16" customHeight="1" spans="1:9">
-      <c r="A35" s="73"/>
-      <c r="B35" s="74"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="78"/>
-    </row>
-    <row r="36" ht="124" customHeight="1" spans="1:9">
-      <c r="A36" s="82"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="86"/>
-    </row>
-    <row r="37" ht="19.5" spans="1:9">
-      <c r="A37" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="88"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="88"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="89" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="90" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="90"/>
-      <c r="D38" s="91" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="92"/>
-      <c r="F38" s="93"/>
-      <c r="G38" s="94" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" s="95"/>
-      <c r="I38" s="96"/>
-    </row>
-    <row r="39" ht="11" customHeight="1" spans="1:9">
-      <c r="A39" s="89"/>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="97"/>
-      <c r="E39" s="98"/>
-      <c r="F39" s="99"/>
-      <c r="G39" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="H39" s="95"/>
-      <c r="I39" s="96"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="36">
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="E9:I9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F32"/>
     <mergeCell ref="H17:H19"/>
     <mergeCell ref="H20:H22"/>
-    <mergeCell ref="H23:H25"/>
     <mergeCell ref="I17:I19"/>
     <mergeCell ref="I20:I22"/>
-    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="A17:C22"/>
     <mergeCell ref="A4:D8"/>
+    <mergeCell ref="E10:I14"/>
     <mergeCell ref="A2:D3"/>
-    <mergeCell ref="E10:I14"/>
-    <mergeCell ref="G28:I29"/>
-    <mergeCell ref="G30:I31"/>
-    <mergeCell ref="G32:I33"/>
-    <mergeCell ref="G34:I35"/>
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="B38:C39"/>
-    <mergeCell ref="A28:E36"/>
-    <mergeCell ref="A17:C22"/>
-    <mergeCell ref="A23:C25"/>
+    <mergeCell ref="G29:I30"/>
+    <mergeCell ref="D35:F36"/>
+    <mergeCell ref="A25:E33"/>
+    <mergeCell ref="G31:I32"/>
+    <mergeCell ref="G25:I26"/>
+    <mergeCell ref="G27:I28"/>
+    <mergeCell ref="B35:C36"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D38" r:id="rId2" display="mahmud@bwsensing.com"/>
+    <hyperlink ref="D35" r:id="rId2" display="mahmud@bwsensing.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.432638888888889" top="0.944444444444444" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" scale="59" orientation="portrait"/>
-  <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2780,7 +2216,7 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2792,6 +2228,6 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/template.xlsx
+++ b/template.xlsx
@@ -649,7 +649,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -817,26 +817,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1050,7 +1030,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="24">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="22">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
@@ -1062,34 +1042,34 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="26">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="27">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="27">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="31">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="29">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="9" borderId="0">
@@ -1174,7 +1154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1257,42 +1237,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1305,8 +1283,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1877,167 +1855,171 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:12">
       <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36">
         <v>1</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40">
+      <c r="F17" s="37"/>
+      <c r="G17" s="38">
         <v>51.47</v>
       </c>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42" t="s">
+      <c r="H17" s="39"/>
+      <c r="I17" s="40" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="33">
         <v>350</v>
       </c>
-      <c r="L17" s="43">
+      <c r="L17" s="41">
         <f t="shared" ref="L17:L25" si="0">K17/$L$16</f>
         <v>51.4705882352941</v>
       </c>
     </row>
     <row r="18" ht="57" customHeight="1" spans="1:12">
-      <c r="A18" s="6"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="38">
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="36">
         <v>4</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40">
+      <c r="F18" s="37"/>
+      <c r="G18" s="38">
         <v>2941.16</v>
       </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
       <c r="K18" s="33">
         <v>300</v>
       </c>
-      <c r="L18" s="43">
+      <c r="L18" s="41">
         <f t="shared" si="0"/>
         <v>44.1176470588235</v>
       </c>
     </row>
     <row r="19" ht="57" customHeight="1" spans="1:12">
-      <c r="A19" s="6"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="38">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="36">
         <v>30</v>
       </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40">
+      <c r="F19" s="37"/>
+      <c r="G19" s="38">
         <f>E19*F19</f>
         <v>0</v>
       </c>
-      <c r="H19" s="45"/>
-      <c r="I19" s="44"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="42"/>
       <c r="K19" s="33">
         <v>200</v>
       </c>
-      <c r="L19" s="43">
+      <c r="L19" s="41">
         <f t="shared" si="0"/>
         <v>29.4117647058824</v>
       </c>
     </row>
     <row r="20" ht="57" customHeight="1" spans="1:12">
-      <c r="A20" s="6"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="38">
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="36">
         <v>1</v>
       </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40">
+      <c r="F20" s="37"/>
+      <c r="G20" s="38">
         <f>E20*F20</f>
         <v>0</v>
       </c>
-      <c r="H20" s="38"/>
-      <c r="I20" s="47"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="45"/>
       <c r="K20" s="33">
         <v>950</v>
       </c>
-      <c r="L20" s="43">
+      <c r="L20" s="41">
         <f t="shared" si="0"/>
         <v>139.705882352941</v>
       </c>
     </row>
     <row r="21" ht="57" customHeight="1" spans="1:12">
-      <c r="A21" s="6"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="38">
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="36">
         <v>10</v>
       </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40">
+      <c r="F21" s="37"/>
+      <c r="G21" s="38">
         <f>E21*F21</f>
         <v>0</v>
       </c>
-      <c r="H21" s="44"/>
-      <c r="I21" s="48"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="46"/>
       <c r="K21" s="33">
         <v>800</v>
       </c>
-      <c r="L21" s="43">
+      <c r="L21" s="41">
         <f t="shared" si="0"/>
         <v>117.647058823529</v>
       </c>
     </row>
     <row r="22" ht="57" customHeight="1" spans="1:12">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="38">
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="36">
         <v>30</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40">
+      <c r="F22" s="37"/>
+      <c r="G22" s="38">
         <f>E22*F22</f>
         <v>0</v>
       </c>
-      <c r="H22" s="45"/>
-      <c r="I22" s="49"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="47"/>
       <c r="K22" s="33">
         <v>650</v>
       </c>
-      <c r="L22" s="43">
+      <c r="L22" s="41">
         <f t="shared" si="0"/>
         <v>95.5882352941177</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="50"/>
+      <c r="A23" s="48"/>
       <c r="I23" s="12"/>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:12">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="52" t="s">
+      <c r="F24" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="53" t="s">
+      <c r="G24" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H24" s="54"/>
+      <c r="H24" s="52"/>
       <c r="I24" s="24"/>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:12">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="53" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="21"/>
-      <c r="F25" s="56" t="s">
+      <c r="F25" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="53" t="s">
+      <c r="G25" s="51" t="s">
         <v>9</v>
       </c>
       <c r="H25" s="3"/>
@@ -2053,10 +2035,10 @@
     <row r="27" ht="13" customHeight="1" spans="1:12">
       <c r="A27" s="6"/>
       <c r="E27" s="16"/>
-      <c r="F27" s="56" t="s">
+      <c r="F27" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="53"/>
+      <c r="G27" s="51"/>
       <c r="H27" s="3"/>
       <c r="I27" s="21"/>
     </row>
@@ -2070,10 +2052,10 @@
     <row r="29" ht="13" customHeight="1" spans="1:12">
       <c r="A29" s="6"/>
       <c r="E29" s="16"/>
-      <c r="F29" s="56" t="s">
+      <c r="F29" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G29" s="53" t="s">
+      <c r="G29" s="51" t="s">
         <v>9</v>
       </c>
       <c r="H29" s="3"/>
@@ -2089,10 +2071,10 @@
     <row r="31" ht="13" customHeight="1" spans="1:12">
       <c r="A31" s="6"/>
       <c r="E31" s="16"/>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="G31" s="53" t="s">
+      <c r="G31" s="51" t="s">
         <v>9</v>
       </c>
       <c r="H31" s="3"/>
@@ -2109,58 +2091,58 @@
     <row r="33" ht="124" customHeight="1" spans="1:9">
       <c r="A33" s="6"/>
       <c r="E33" s="16"/>
-      <c r="F33" s="58" t="s">
+      <c r="F33" s="56" t="s">
         <v>33</v>
       </c>
       <c r="I33" s="16"/>
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:9">
-      <c r="A34" s="59" t="s">
+      <c r="A34" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="54"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
       <c r="I34" s="24"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="61" t="s">
+      <c r="B35" s="59" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="21"/>
-      <c r="D35" s="62" t="s">
+      <c r="D35" s="60" t="s">
         <v>37</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="21"/>
-      <c r="G35" s="63" t="s">
+      <c r="G35" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="54"/>
+      <c r="H35" s="52"/>
       <c r="I35" s="24"/>
     </row>
     <row r="36" ht="11" customHeight="1" spans="1:9">
-      <c r="A36" s="45"/>
+      <c r="A36" s="43"/>
       <c r="B36" s="27"/>
       <c r="C36" s="29"/>
       <c r="D36" s="27"/>
       <c r="E36" s="28"/>
       <c r="F36" s="29"/>
-      <c r="G36" s="63" t="s">
+      <c r="G36" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="54"/>
+      <c r="H36" s="52"/>
       <c r="I36" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="E9:I9"/>
     <mergeCell ref="B10:C10"/>
@@ -2186,7 +2168,6 @@
     <mergeCell ref="H20:H22"/>
     <mergeCell ref="I17:I19"/>
     <mergeCell ref="I20:I22"/>
-    <mergeCell ref="A17:C22"/>
     <mergeCell ref="A4:D8"/>
     <mergeCell ref="E10:I14"/>
     <mergeCell ref="A2:D3"/>
@@ -2197,6 +2178,8 @@
     <mergeCell ref="G25:I26"/>
     <mergeCell ref="G27:I28"/>
     <mergeCell ref="B35:C36"/>
+    <mergeCell ref="A17:C19"/>
+    <mergeCell ref="A20:C22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D35" r:id="rId2" display="mahmud@bwsensing.com"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>Wuxi Bewis Sensing Technology LLC</t>
   </si>
@@ -46,13 +46,7 @@
     <t>Valid Until:</t>
   </si>
   <si>
-    <t>July,27th.2025</t>
-  </si>
-  <si>
     <t>Quote Number:</t>
-  </si>
-  <si>
-    <t>20260514-MC-BD</t>
   </si>
   <si>
     <t>Customer ID</t>
@@ -168,7 +162,7 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="\$#,##0.00;[Red]\-\$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="40">
@@ -1730,28 +1724,24 @@
         <v>4</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="10" t="s">
-        <v>5</v>
-      </c>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:12">
       <c r="A6" s="6"/>
       <c r="G6" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:12">
       <c r="A7" s="6"/>
       <c r="G7" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="8" customHeight="1" spans="1:12">
@@ -1760,22 +1750,22 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:12">
       <c r="A9" s="13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I9" s="16"/>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:12">
       <c r="A10" s="17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="19"/>
       <c r="E10" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -1784,7 +1774,7 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:12">
       <c r="A11" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
@@ -1793,7 +1783,7 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:12">
       <c r="A12" s="22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="24"/>
@@ -1802,7 +1792,7 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:12">
       <c r="A13" s="22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="24"/>
@@ -1811,7 +1801,7 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:12">
       <c r="A14" s="22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="26"/>
@@ -1828,25 +1818,25 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:12">
       <c r="A16" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="F16" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="G16" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="H16" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="I16" s="32" t="s">
         <v>22</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>24</v>
       </c>
       <c r="K16" s="33"/>
       <c r="L16" s="33">
@@ -1858,16 +1848,15 @@
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
       <c r="D17" s="35"/>
-      <c r="E17" s="36">
-        <v>1</v>
-      </c>
+      <c r="E17" s="36"/>
       <c r="F17" s="37"/>
       <c r="G17" s="38">
-        <v>51.47</v>
+        <f>E17*F17</f>
+        <v>0</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K17" s="33">
         <v>350</v>
@@ -1882,12 +1871,11 @@
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
       <c r="D18" s="42"/>
-      <c r="E18" s="36">
-        <v>4</v>
-      </c>
+      <c r="E18" s="36"/>
       <c r="F18" s="37"/>
       <c r="G18" s="38">
-        <v>2941.16</v>
+        <f>E18*F18</f>
+        <v>0</v>
       </c>
       <c r="H18" s="42"/>
       <c r="I18" s="42"/>
@@ -1904,9 +1892,7 @@
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="36">
-        <v>30</v>
-      </c>
+      <c r="E19" s="36"/>
       <c r="F19" s="37"/>
       <c r="G19" s="38">
         <f>E19*F19</f>
@@ -1927,9 +1913,7 @@
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
       <c r="D20" s="44"/>
-      <c r="E20" s="36">
-        <v>1</v>
-      </c>
+      <c r="E20" s="36"/>
       <c r="F20" s="37"/>
       <c r="G20" s="38">
         <f>E20*F20</f>
@@ -1950,9 +1934,7 @@
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
       <c r="D21" s="42"/>
-      <c r="E21" s="36">
-        <v>10</v>
-      </c>
+      <c r="E21" s="36"/>
       <c r="F21" s="37"/>
       <c r="G21" s="38">
         <f>E21*F21</f>
@@ -1973,9 +1955,7 @@
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
       <c r="D22" s="43"/>
-      <c r="E22" s="36">
-        <v>30</v>
-      </c>
+      <c r="E22" s="36"/>
       <c r="F22" s="37"/>
       <c r="G22" s="38">
         <f>E22*F22</f>
@@ -1997,30 +1977,30 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:12">
       <c r="A24" s="49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H24" s="52"/>
       <c r="I24" s="24"/>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:12">
       <c r="A25" s="53" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="21"/>
       <c r="F25" s="54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="21"/>
@@ -2036,7 +2016,7 @@
       <c r="A27" s="6"/>
       <c r="E27" s="16"/>
       <c r="F27" s="54" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="51"/>
       <c r="H27" s="3"/>
@@ -2053,10 +2033,10 @@
       <c r="A29" s="6"/>
       <c r="E29" s="16"/>
       <c r="F29" s="54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="21"/>
@@ -2072,10 +2052,10 @@
       <c r="A31" s="6"/>
       <c r="E31" s="16"/>
       <c r="F31" s="55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="21"/>
@@ -2092,13 +2072,13 @@
       <c r="A33" s="6"/>
       <c r="E33" s="16"/>
       <c r="F33" s="56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I33" s="16"/>
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:9">
       <c r="A34" s="57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B34" s="52"/>
       <c r="C34" s="52"/>
@@ -2111,19 +2091,19 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="60" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="21"/>
       <c r="G35" s="61" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H35" s="52"/>
       <c r="I35" s="24"/>
@@ -2136,7 +2116,7 @@
       <c r="E36" s="28"/>
       <c r="F36" s="29"/>
       <c r="G36" s="61" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H36" s="52"/>
       <c r="I36" s="24"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -643,7 +643,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -833,60 +833,8 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -898,6 +846,19 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1024,7 +985,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="22">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="19">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
@@ -1036,34 +997,34 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="26">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="27">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="29">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="26">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="9" borderId="0">
@@ -1148,7 +1109,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1249,22 +1210,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1277,8 +1231,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1674,7 +1628,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.9" style="1" customWidth="1"/>
@@ -1862,7 +1816,7 @@
         <v>350</v>
       </c>
       <c r="L17" s="41">
-        <f t="shared" ref="L17:L25" si="0">K17/$L$16</f>
+        <f>K17/$L$16</f>
         <v>51.4705882352941</v>
       </c>
     </row>
@@ -1878,12 +1832,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
+      <c r="I18" s="43"/>
       <c r="K18" s="33">
         <v>300</v>
       </c>
       <c r="L18" s="41">
-        <f t="shared" si="0"/>
+        <f>K18/$L$16</f>
         <v>44.1176470588235</v>
       </c>
     </row>
@@ -1891,238 +1845,175 @@
       <c r="A19" s="34"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
-      <c r="D19" s="43"/>
+      <c r="D19" s="44"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
       <c r="G19" s="38">
         <f>E19*F19</f>
         <v>0</v>
       </c>
-      <c r="H19" s="43"/>
-      <c r="I19" s="42"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="43"/>
       <c r="K19" s="33">
         <v>200</v>
       </c>
       <c r="L19" s="41">
-        <f t="shared" si="0"/>
+        <f>K19/$L$16</f>
         <v>29.4117647058824</v>
       </c>
     </row>
-    <row r="20" ht="57" customHeight="1" spans="1:12">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38">
-        <f>E20*F20</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="45"/>
-      <c r="K20" s="33">
-        <v>950</v>
-      </c>
-      <c r="L20" s="41">
-        <f t="shared" si="0"/>
-        <v>139.705882352941</v>
-      </c>
-    </row>
-    <row r="21" ht="57" customHeight="1" spans="1:12">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38">
-        <f>E21*F21</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="42"/>
-      <c r="I21" s="46"/>
-      <c r="K21" s="33">
-        <v>800</v>
-      </c>
-      <c r="L21" s="41">
-        <f t="shared" si="0"/>
-        <v>117.647058823529</v>
-      </c>
-    </row>
-    <row r="22" ht="57" customHeight="1" spans="1:12">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38">
-        <f>E22*F22</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="43"/>
-      <c r="I22" s="47"/>
-      <c r="K22" s="33">
-        <v>650</v>
-      </c>
-      <c r="L22" s="41">
-        <f t="shared" si="0"/>
-        <v>95.5882352941177</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="48"/>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:12">
-      <c r="A24" s="49" t="s">
+    <row r="20" spans="1:12">
+      <c r="A20" s="45"/>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:12">
+      <c r="A21" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F21" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="51" t="s">
+      <c r="G21" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="52"/>
-      <c r="I24" s="24"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="24"/>
+    </row>
+    <row r="22" ht="13" customHeight="1" spans="1:12">
+      <c r="A22" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="21"/>
+    </row>
+    <row r="23" ht="13" customHeight="1" spans="1:12">
+      <c r="A23" s="6"/>
+      <c r="E23" s="16"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+    </row>
+    <row r="24" ht="13" customHeight="1" spans="1:12">
+      <c r="A24" s="6"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="48"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="21"/>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:12">
-      <c r="A25" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="21"/>
+      <c r="A25" s="6"/>
+      <c r="E25" s="16"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:12">
       <c r="A26" s="6"/>
       <c r="E26" s="16"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="29"/>
+      <c r="F26" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="21"/>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:12">
       <c r="A27" s="6"/>
       <c r="E27" s="16"/>
-      <c r="F27" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="51"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="21"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="29"/>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:12">
       <c r="A28" s="6"/>
       <c r="E28" s="16"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29"/>
-    </row>
-    <row r="29" ht="13" customHeight="1" spans="1:12">
+      <c r="F28" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="21"/>
+    </row>
+    <row r="29" ht="16" customHeight="1" spans="1:12">
       <c r="A29" s="6"/>
       <c r="E29" s="16"/>
-      <c r="F29" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="21"/>
-    </row>
-    <row r="30" ht="13" customHeight="1" spans="1:12">
+      <c r="F29" s="28"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="29"/>
+    </row>
+    <row r="30" ht="124" customHeight="1" spans="1:12">
       <c r="A30" s="6"/>
       <c r="E30" s="16"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="29"/>
-    </row>
-    <row r="31" ht="13" customHeight="1" spans="1:12">
-      <c r="A31" s="6"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="21"/>
-    </row>
-    <row r="32" ht="16" customHeight="1" spans="1:12">
-      <c r="A32" s="6"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="29"/>
-    </row>
-    <row r="33" ht="124" customHeight="1" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="56" t="s">
+      <c r="F30" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="I33" s="16"/>
-    </row>
-    <row r="34" ht="19.5" customHeight="1" spans="1:9">
-      <c r="A34" s="57" t="s">
+      <c r="I30" s="16"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1" spans="1:12">
+      <c r="A31" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="58" t="s">
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="24"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="59" t="s">
+      <c r="B32" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="60" t="s">
+      <c r="C32" s="21"/>
+      <c r="D32" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="61" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="52"/>
-      <c r="I35" s="24"/>
-    </row>
-    <row r="36" ht="11" customHeight="1" spans="1:9">
-      <c r="A36" s="43"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="61" t="s">
+      <c r="H32" s="49"/>
+      <c r="I32" s="24"/>
+    </row>
+    <row r="33" ht="11" customHeight="1" spans="1:9">
+      <c r="A33" s="44"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="H36" s="52"/>
-      <c r="I36" s="24"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="33">
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="E9:I9"/>
     <mergeCell ref="B10:C10"/>
@@ -2131,38 +2022,34 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="A32:A33"/>
     <mergeCell ref="D17:D19"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
     <mergeCell ref="H17:H19"/>
-    <mergeCell ref="H20:H22"/>
     <mergeCell ref="I17:I19"/>
-    <mergeCell ref="I20:I22"/>
     <mergeCell ref="A4:D8"/>
     <mergeCell ref="E10:I14"/>
     <mergeCell ref="A2:D3"/>
-    <mergeCell ref="G29:I30"/>
-    <mergeCell ref="D35:F36"/>
-    <mergeCell ref="A25:E33"/>
-    <mergeCell ref="G31:I32"/>
-    <mergeCell ref="G25:I26"/>
-    <mergeCell ref="G27:I28"/>
-    <mergeCell ref="B35:C36"/>
     <mergeCell ref="A17:C19"/>
-    <mergeCell ref="A20:C22"/>
+    <mergeCell ref="G26:I27"/>
+    <mergeCell ref="D32:F33"/>
+    <mergeCell ref="A22:E30"/>
+    <mergeCell ref="G28:I29"/>
+    <mergeCell ref="G22:I23"/>
+    <mergeCell ref="G24:I25"/>
+    <mergeCell ref="B32:C33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D35" r:id="rId2" display="mahmud@bwsensing.com"/>
+    <hyperlink ref="D32" r:id="rId2" display="mahmud@bwsensing.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.432638888888889" top="0.944444444444444" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" scale="59" orientation="portrait"/>
